--- a/data/trans_orig/P79A10_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A10_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14417</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20503</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28211</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>43478</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>43478</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>43478</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,44 +1436,44 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>89,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>43,27%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1570</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3684</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -1524,69 +1524,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3777</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>56,73%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3684</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,38%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>833</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>833</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2818,27 +2818,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>90043</t>
+          <t>103438</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85229</t>
+          <t>98139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92196</t>
+          <t>105810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>82829</t>
+          <t>95640</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78435</t>
+          <t>91064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85172</t>
+          <t>98511</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>172872</t>
+          <t>199078</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166811</t>
+          <t>192766</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176211</t>
+          <t>203251</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>106478</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>106478</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>106478</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>86685</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>86685</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86685</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>179506</t>
+          <t>206436</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>179506</t>
+          <t>206436</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>179506</t>
+          <t>206436</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>111250</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120296</t>
+          <t>138862</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>103497</t>
+          <t>120360</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>108837</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111253</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>214748</t>
+          <t>248009</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>196269</t>
+          <t>229941</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>227843</t>
+          <t>261933</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>29957</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>54549</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
